--- a/backend/data/price_inputs/price_template.xlsx
+++ b/backend/data/price_inputs/price_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tequi\OneDrive\桌面\CPIforecast\backend\data\price_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A23554F-27E1-4695-A07B-84B17279C698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613752F1-9438-424F-A10B-026424CE0B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="430" windowWidth="14280" windowHeight="9250" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8450" yWindow="1800" windowWidth="17430" windowHeight="9250" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="說明" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="yyyy/m"/>
+    <numFmt numFmtId="176" formatCode="yyyy/m"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -722,13 +722,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - 輔色1 2" xfId="2" xr:uid="{3C3A41F4-C3FC-4C8B-A54B-D7CB81A65383}"/>
@@ -1199,7 +1199,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E180"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" style="6" customWidth="1"/>
@@ -3192,6 +3192,17 @@
         <v>44.411999999999999</v>
       </c>
     </row>
+    <row r="181" spans="1:3">
+      <c r="A181" s="5">
+        <v>46143</v>
+      </c>
+      <c r="B181">
+        <v>29.657999999999998</v>
+      </c>
+      <c r="C181">
+        <v>43.253999999999998</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
